--- a/12628121.xlsx
+++ b/12628121.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0cd0ce09f5db97cd/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0cd0ce09f5db97cd/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1333120-15CD-4AA6-A7BF-C330CE599694}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87143E9E-ABF7-4126-8F9B-8FC941A56E01}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,15 @@
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -26,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -198,6 +207,15 @@
   <si>
     <t>Neutral</t>
   </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
+  </si>
 </sst>
 </file>
 
@@ -308,7 +326,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -331,11 +349,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -375,6 +404,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -864,72 +896,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="21">
         <v>12628121</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -1066,69 +1098,135 @@
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46246</v>
+      </c>
+      <c r="B8" s="14">
+        <v>420</v>
+      </c>
+      <c r="C8" s="14">
+        <v>0</v>
+      </c>
+      <c r="D8" s="14">
+        <v>0</v>
+      </c>
+      <c r="E8" s="14">
+        <v>0</v>
+      </c>
+      <c r="F8" s="14">
+        <v>350</v>
+      </c>
+      <c r="G8" s="14">
+        <v>7</v>
+      </c>
+      <c r="H8" s="14">
+        <v>150</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>520</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B9" s="14">
+        <v>420</v>
+      </c>
+      <c r="C9" s="14">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14">
+        <v>0</v>
+      </c>
+      <c r="E9" s="14">
+        <v>0</v>
+      </c>
+      <c r="F9" s="14">
+        <v>150</v>
+      </c>
+      <c r="G9" s="14">
+        <v>3</v>
+      </c>
+      <c r="H9" s="18">
+        <v>150</v>
+      </c>
+      <c r="I9" s="15">
+        <f>IF(SUM(B9:F9,H9)=0,"",SUM(B9:F9,H9))</f>
+        <v>720</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
+        <v>720</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46248</v>
+      </c>
+      <c r="B10" s="14">
+        <v>480</v>
+      </c>
+      <c r="C10" s="14">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14">
+        <v>0</v>
+      </c>
+      <c r="E10" s="14">
+        <v>0</v>
+      </c>
+      <c r="F10" s="14">
+        <v>300</v>
+      </c>
+      <c r="G10" s="14">
+        <v>6</v>
+      </c>
+      <c r="H10" s="14">
+        <v>150</v>
+      </c>
+      <c r="I10" s="15">
+        <f>IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
+        <v>930</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
+        <v>510</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">

--- a/12628121.xlsx
+++ b/12628121.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0cd0ce09f5db97cd/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87143E9E-ABF7-4126-8F9B-8FC941A56E01}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C3C6359-0723-4A01-8123-4B701C506D26}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1230,91 +1230,179 @@
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46249</v>
+      </c>
+      <c r="B11" s="14">
+        <v>420</v>
+      </c>
+      <c r="C11" s="14">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>90</v>
+      </c>
+      <c r="E11" s="14">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>150</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
+        <v>780</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46250</v>
+      </c>
+      <c r="B12" s="14">
+        <v>420</v>
+      </c>
+      <c r="C12" s="14">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <v>0</v>
+      </c>
+      <c r="E12" s="14">
+        <v>0</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>150</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>570</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+        <v>870</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B13" s="14">
+        <v>420</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>0</v>
+      </c>
+      <c r="E13" s="14">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14">
+        <v>350</v>
+      </c>
+      <c r="G13" s="14">
+        <v>7</v>
+      </c>
+      <c r="H13" s="14">
+        <v>150</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+        <v>520</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B14" s="14">
+        <v>480</v>
+      </c>
+      <c r="C14" s="14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="14">
+        <v>0</v>
+      </c>
+      <c r="E14" s="14">
+        <v>0</v>
+      </c>
+      <c r="F14" s="14">
+        <v>200</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="14">
+        <v>150</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
